--- a/tools/importer/reports/import-merkle-now.report.xlsx
+++ b/tools/importer/reports/import-merkle-now.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="30">
   <si>
     <t>_reportFile</t>
   </si>
@@ -64,34 +64,37 @@
     <t>en/merkle-now.report.json</t>
   </si>
   <si>
+    <t>["column-control","content-filter"]</t>
+  </si>
+  <si>
+    <t>en/merkle-now</t>
+  </si>
+  <si>
+    <t>merkle-now</t>
+  </si>
+  <si>
+    <t>2026-09-17T04:56:33.967Z</t>
+  </si>
+  <si>
+    <t>Merkle Now: Thought Leadership, Culture &amp; Resources</t>
+  </si>
+  <si>
+    <t>https://www.merkle.com/en/merkle-now.html</t>
+  </si>
+  <si>
+    <t>en/work.report.json</t>
+  </si>
+  <si>
     <t>["carousel-cases","content-filter"]</t>
   </si>
   <si>
-    <t>en/merkle-now</t>
-  </si>
-  <si>
-    <t>merkle-now</t>
-  </si>
-  <si>
-    <t>2026-09-16T12:57:26.158Z</t>
-  </si>
-  <si>
-    <t>Merkle Now: Thought Leadership, Culture &amp; Resources</t>
-  </si>
-  <si>
-    <t>https://www.merkle.com/en/merkle-now.html</t>
-  </si>
-  <si>
-    <t>en/work.report.json</t>
-  </si>
-  <si>
     <t>en/work</t>
   </si>
   <si>
     <t>work</t>
   </si>
   <si>
-    <t>2026-09-16T12:50:51.050Z</t>
+    <t>2026-09-16T12:57:34.193Z</t>
   </si>
   <si>
     <t>Customer Experience Case Studies &amp; Client Stories | Merkle</t>
@@ -581,25 +584,25 @@
         <v>23</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D4" t="s">
         <v>11</v>
       </c>
       <c r="E4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/tools/importer/reports/import-merkle-now.report.xlsx
+++ b/tools/importer/reports/import-merkle-now.report.xlsx
@@ -64,7 +64,7 @@
     <t>en/merkle-now.report.json</t>
   </si>
   <si>
-    <t>["column-control","content-filter"]</t>
+    <t>["column-control"]</t>
   </si>
   <si>
     <t>en/merkle-now</t>
@@ -73,7 +73,7 @@
     <t>merkle-now</t>
   </si>
   <si>
-    <t>2026-09-17T04:56:33.967Z</t>
+    <t>2026-09-17T05:53:46.674Z</t>
   </si>
   <si>
     <t>Merkle Now: Thought Leadership, Culture &amp; Resources</t>

--- a/tools/importer/reports/import-merkle-now.report.xlsx
+++ b/tools/importer/reports/import-merkle-now.report.xlsx
@@ -64,7 +64,7 @@
     <t>en/merkle-now.report.json</t>
   </si>
   <si>
-    <t>["column-control"]</t>
+    <t>["columns-control"]</t>
   </si>
   <si>
     <t>en/merkle-now</t>
@@ -73,7 +73,7 @@
     <t>merkle-now</t>
   </si>
   <si>
-    <t>2026-09-17T05:53:46.674Z</t>
+    <t>2026-09-17T06:39:57.072Z</t>
   </si>
   <si>
     <t>Merkle Now: Thought Leadership, Culture &amp; Resources</t>

--- a/tools/importer/reports/import-merkle-now.report.xlsx
+++ b/tools/importer/reports/import-merkle-now.report.xlsx
@@ -64,7 +64,7 @@
     <t>en/merkle-now.report.json</t>
   </si>
   <si>
-    <t>["columns-control"]</t>
+    <t>["columns"]</t>
   </si>
   <si>
     <t>en/merkle-now</t>
@@ -73,7 +73,7 @@
     <t>merkle-now</t>
   </si>
   <si>
-    <t>2026-09-17T06:39:57.072Z</t>
+    <t>2026-09-17T07:51:47.754Z</t>
   </si>
   <si>
     <t>Merkle Now: Thought Leadership, Culture &amp; Resources</t>
